--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/PENNSYLVANIA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/PENNSYLVANIA_2020.xlsx
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>San Simon De Guerero</t>
+          <t>San Simon De Guerrero</t>
         </is>
       </c>
       <c r="C119">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C142">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C149">
@@ -4297,7 +4297,7 @@
         <v>30</v>
       </c>
       <c r="D219">
-        <v>0.009308098045299411</v>
+        <v>0.009308098045299413</v>
       </c>
     </row>
     <row r="220">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Santiago Tulantepec De Lugo Guerero</t>
+          <t>Santiago Tulantepec De Lugo Guerrero</t>
         </is>
       </c>
       <c r="C255">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C373">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C402">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Ayotoxco De Guerero</t>
+          <t>Ayotoxco De Guerrero</t>
         </is>
       </c>
       <c r="C449">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C477">
